--- a/src/attributions/attributions_ig_traj_110.xlsx
+++ b/src/attributions/attributions_ig_traj_110.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG16"/>
+  <dimension ref="A1:GG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2137,10 +2137,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.04020525715288818</v>
+        <v>0.04159287848202702</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.539030569316518e-05</v>
+        <v>0.008440418380720542</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.03356953387055896</v>
+        <v>-0.04144532164567587</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -2164,37 +2164,37 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01770220294621074</v>
+        <v>0.08795211972316949</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01071269482235521</v>
+        <v>0.01079667915524374</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.05079758279273062</v>
+        <v>-0.05539782207514155</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.716671894178242e-12</v>
+        <v>-2.057706208612745e-11</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00111064927879385</v>
+        <v>0.009923369329145509</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.003255268942080183</v>
+        <v>0.008506228278350195</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01842645698459048</v>
+        <v>-0.04889572736770004</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02827153757390061</v>
+        <v>-0.02668185075864883</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.004667477724573199</v>
+        <v>-0.03633186539586487</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.0002869043249560763</v>
+        <v>-0.001292700289420636</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01575631723213498</v>
+        <v>-0.0290809729733326</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.005388186738737187</v>
+        <v>-0.01479082040722377</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.05500074948865701</v>
+        <v>0.1715316927782434</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
@@ -2284,79 +2284,79 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.01101541687937099</v>
+        <v>-0.006285584016369575</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.05147670902227387</v>
+        <v>-0.02821732336399286</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01955047523015926</v>
+        <v>-0.02179444489186274</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.02267648725603328</v>
+        <v>-0.02492388055308056</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.0253828626879316</v>
+        <v>-0.03278604645614019</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02579107011672319</v>
+        <v>0.02786416225771881</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0006230787990622092</v>
+        <v>0.05291452447994387</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01317166286774797</v>
+        <v>0.05314803861349939</v>
       </c>
       <c r="BR4" t="n">
         <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.007994424922589843</v>
+        <v>0.01749781703289767</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,10 +2365,10 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.005717296330884951</v>
+        <v>-0.01741442209767174</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.0001897235409686158</v>
+        <v>-0.02537217170445298</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
@@ -2380,49 +2380,49 @@
         <v>-0</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.005617686693106653</v>
+        <v>-0.01905990233025421</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.004206358403014273</v>
+        <v>-0.009583923577566577</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.03163893276563843</v>
+        <v>0.04270362496804626</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.01931925861857461</v>
+        <v>-0.03208386621093389</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.02266849105206237</v>
+        <v>0.04231730613860522</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.006453458217411562</v>
+        <v>0.0186385948682645</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
@@ -2431,52 +2431,52 @@
         <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.002048535951390471</v>
+        <v>-0.02480203710620394</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.00536719917260492</v>
+        <v>-0.01306208961030687</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.02742564950296803</v>
+        <v>0.04112715613584058</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.01421799048045172</v>
+        <v>-0.01421332023229229</v>
       </c>
       <c r="DG4" t="n">
         <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.003404629143420892</v>
+        <v>-0.03271984630452134</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.06588567358228825</v>
+        <v>0.005863078636541531</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,52 +2485,52 @@
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.003295237127693308</v>
+        <v>-0.01116522895156023</v>
       </c>
       <c r="DP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0002405232928225424</v>
+        <v>0.03409040299720214</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.001996678485799956</v>
+        <v>0.06551886355662695</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.009756848932985325</v>
+        <v>-0.0008163278719880083</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.01315438850810774</v>
+        <v>0.0241038285163582</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.02601492891667376</v>
+        <v>-0.04459027176683949</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2542,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.003188406334159844</v>
+        <v>-0.0451897782203654</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
@@ -2554,37 +2554,37 @@
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.002553030121969357</v>
+        <v>-0.03151106468084573</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01013249268018621</v>
+        <v>0.01196690490530115</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.002247598808844059</v>
+        <v>0.0182345956332652</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.0003793074045038354</v>
+        <v>0.001793670141906142</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0367907805275213</v>
+        <v>0.02967044006921879</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.003481807415146848</v>
+        <v>-0.02711242577116032</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,25 +2608,25 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.002008635817204684</v>
+        <v>-0.02119732244561862</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.02710536637314676</v>
+        <v>0.03776687089535695</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
         <v>-0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.007932071876933349</v>
+        <v>-0.03699533769471131</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,10 +2635,10 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.02363323450132443</v>
+        <v>-0.008058018020125018</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.003248273197868324</v>
+        <v>-0.01628589037913396</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.004606613381517554</v>
+        <v>0.01052561578812127</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.004223264140921479</v>
+        <v>0.01120873658282744</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03937953604688487</v>
+        <v>0.03155005633942688</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,25 +2674,25 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02212943976739651</v>
+        <v>0.005521919534494628</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.001437069410592925</v>
+        <v>0.03688228029447894</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,57 +2701,57 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3186647374652557</v>
+        <v>0.1192878791861783</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2178488818413104</v>
+        <v>-0.1123271426984444</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.09278233783254852</v>
+        <v>-0.02646174264271778</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2496904430488794</v>
+        <v>0.1265326580228481</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1706966271898363</v>
+        <v>-0.1325628970421132</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.09558195397736763</v>
+        <v>-0.02372886169301261</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2760,22 +2760,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01041694203971072</v>
+        <v>-0.0005262506622297977</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.005224035196026768</v>
+        <v>-0.006698102615036737</v>
       </c>
       <c r="W5" t="n">
-        <v>-4.860173440662108e-11</v>
+        <v>-5.15824286767213e-11</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
@@ -2790,43 +2790,43 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.111054660835876</v>
+        <v>0.006210190522279684</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.04325879912187421</v>
+        <v>-0.005385949020397995</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02536601463514855</v>
+        <v>-0.03523269181172402</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.04561968820171319</v>
+        <v>0.05284556848367818</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.05176323285785972</v>
+        <v>-0.06848308628786182</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.07140329866450552</v>
+        <v>0.002255628779477134</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2841,22 +2841,22 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.5127980504822093</v>
+        <v>0.2235453500199118</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.0961648994529052</v>
+        <v>-0.1153855650196557</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0559175913476542</v>
+        <v>-0.03006112259547567</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2865,22 +2865,22 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01369758287745563</v>
+        <v>-0.01069950826211626</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.1053622798146032</v>
+        <v>-0.01510700722293542</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1548974546345803</v>
+        <v>-0.03546963043038245</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.06397195778865046</v>
+        <v>-0.01191301419398422</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.1009153714373914</v>
+        <v>0.002134621071199921</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.07057360787657072</v>
+        <v>0.0889465940616903</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,22 +2925,22 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1093246101562668</v>
+        <v>0.04089908199425982</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.02261273644275602</v>
+        <v>0.03035821425152922</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.02348798109685666</v>
+        <v>-0.02113714981963611</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
@@ -2949,109 +2949,109 @@
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1219150542754004</v>
+        <v>-0.08351609462541669</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.04717652592477912</v>
+        <v>0.05665385438269565</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.009026969769910579</v>
+        <v>0.02705428141922751</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.04661932692982941</v>
+        <v>-0.06912951642055946</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.07000514783763057</v>
+        <v>0.09278856272592566</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1224440390342072</v>
+        <v>0.0429001113641226</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT5" t="n">
         <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1125400378702934</v>
+        <v>-0.08761690476827541</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.07616985876696217</v>
+        <v>0.06193745972181925</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01209300788021014</v>
+        <v>0.0209004274775392</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.004954191407515898</v>
+        <v>-0.002849677671453367</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.06300757236345993</v>
+        <v>0.01304265492495367</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.03420944098624957</v>
+        <v>-0.01526749769563321</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
         <v>0</v>
@@ -3060,19 +3060,19 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.1318226003118586</v>
+        <v>-0.05014345027075542</v>
       </c>
       <c r="DP5" t="n">
         <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.02719307700883965</v>
+        <v>0.02266197588771587</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.05960563924906352</v>
+        <v>-0.03376976744366291</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>0</v>
@@ -3084,28 +3084,28 @@
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-9.868866400715262e-05</v>
+        <v>0.0312529443171379</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.01087783087648027</v>
+        <v>0.09656843105846562</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.05883989265108791</v>
+        <v>-0.01297972392404384</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,22 +3114,22 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.04503908994869547</v>
+        <v>-0.06783300247155173</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.02985821422875153</v>
+        <v>0.03273247030399734</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.08417970368546822</v>
+        <v>0.00699433432137837</v>
       </c>
       <c r="EK5" t="n">
         <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
@@ -3141,22 +3141,22 @@
         <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.09889318246479112</v>
+        <v>-0.0320164589265103</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.09006347834878829</v>
+        <v>0.04392119189725097</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.02095781225555955</v>
+        <v>0.02856090961386349</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3168,43 +3168,43 @@
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1133968469025229</v>
+        <v>-0.09453959556604143</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.08178867389636366</v>
+        <v>0.05956996270588098</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.01418184450213094</v>
+        <v>0.01521726564711167</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.01498118458119499</v>
+        <v>-0.04763126159736523</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.07191409704112904</v>
+        <v>0.04021757316645502</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.100633066590807</v>
+        <v>0.04290838928446707</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
@@ -3219,19 +3219,19 @@
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>4.023417282264915e-05</v>
+        <v>0.03806497131344318</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.1121104778169222</v>
+        <v>0.151090140584752</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.1260704474634167</v>
+        <v>-0.02284936747940205</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
@@ -3246,39 +3246,39 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.003834608765523169</v>
+        <v>-0.07587458960129113</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.02861326589252225</v>
+        <v>-0.003412833264237314</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02035807396164853</v>
+        <v>0.03415531196395695</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,10 +3287,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01577308934551525</v>
+        <v>0.01409542710069132</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.003545981244043232</v>
+        <v>-0.008944869719630204</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005219642031833855</v>
+        <v>0.06484439604259644</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,16 +3314,16 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.02330986765162957</v>
+        <v>0.003224260738736667</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01268520596737228</v>
+        <v>-0.02118690832505732</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -3332,130 +3332,130 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005020873463182201</v>
+        <v>-0.001727404705487853</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0006403567090241751</v>
+        <v>-0.002600519632169943</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.003111279759211004</v>
+        <v>0.0003666529819029935</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02554151713068461</v>
+        <v>-0.03195035663927734</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.03211811959998435</v>
+        <v>-0.03735987237683846</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.003112484570060748</v>
+        <v>-0.01511870617070419</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.001466975932429229</v>
+        <v>0.002290276031067171</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01536886183427545</v>
+        <v>-0.006510782994618382</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.00338091613506879</v>
+        <v>-0.01518589096939765</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.05804243716078446</v>
+        <v>0.09808791077467313</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.02508749961178434</v>
+        <v>-0.02323027853672367</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0012014213777302</v>
+        <v>-0.02632053515922112</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.004997648244797071</v>
+        <v>-0.009439704131476628</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.02661498944116844</v>
+        <v>-0.01081833901216084</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.006458865157252408</v>
+        <v>-0.01269983164395531</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,37 +3464,37 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02454532846232993</v>
+        <v>0.02235156920043389</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0111560083368755</v>
+        <v>0.04098202105279296</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01639801505045322</v>
+        <v>0.02394979647710142</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.006983636438968887</v>
+        <v>0.01503488425862765</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.003616043278169391</v>
+        <v>-0.003154608518684077</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.007314653205488022</v>
+        <v>-0.01349021915362483</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,7 +3521,7 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.0002047697464481218</v>
+        <v>-0.009339845328808726</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
@@ -3530,16 +3530,16 @@
         <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0006214144932991432</v>
+        <v>-0.004682509012326795</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.008108823802771429</v>
+        <v>0.02397556869780834</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
@@ -3548,52 +3548,52 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.00654286503486187</v>
+        <v>-0.01910096445459512</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.00804902756113739</v>
+        <v>0.03276337544549328</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01271126431749344</v>
+        <v>0.01898677427346329</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.005544679635142979</v>
+        <v>-0.01195855947869305</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.002086227215759019</v>
+        <v>-0.00470079192962088</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.006163450047291553</v>
+        <v>0.0212428284666464</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
@@ -3602,19 +3602,19 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.006032833905101002</v>
+        <v>-0.01437822422371783</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0003339607554535736</v>
+        <v>-0.001360549523979831</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01976969109352376</v>
+        <v>0.01107628047416179</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,121 +3623,121 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.01367330672331159</v>
+        <v>-0.004769925069443956</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.008617214582224364</v>
+        <v>-0.0001488395187046005</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.007709921057115193</v>
+        <v>0.0312169048852947</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01046688006799151</v>
+        <v>-0.01823211825437745</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.01173153403112686</v>
+        <v>0.0182990845765687</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.001606021186241069</v>
+        <v>0.02327817908867115</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.0005175244937288742</v>
+        <v>-0.0178724846081992</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.005821114876627361</v>
+        <v>-0.01453086439561228</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0006480603224586097</v>
+        <v>0.004494971100291951</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.002101443086528412</v>
+        <v>0.001139152019744031</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01075468734997757</v>
+        <v>-0.008588479691146799</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03417483195974765</v>
+        <v>0.01475811491478509</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.002935536245500001</v>
+        <v>-0.01628027517248824</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,52 +3746,52 @@
         <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.00248021830271213</v>
+        <v>-0.01248129138327995</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.009234888963657116</v>
+        <v>0.01932984036472734</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.0124540824353646</v>
+        <v>-0.03094520542303323</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.0164230026439754</v>
+        <v>0.02795049469360008</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02188211033121587</v>
+        <v>0.0007455731372913177</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.004555123315662045</v>
+        <v>0.009038019617487396</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.003013131815799797</v>
+        <v>0.002481892723500594</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.004474622302705079</v>
+        <v>-0.01305778767897947</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,25 +3812,25 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.0268527739188738</v>
+        <v>0.005719313257027397</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.003878768689804752</v>
+        <v>0.02013515978551853</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.154551305382427</v>
+        <v>0.04218462267561395</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.03086337986528205</v>
+        <v>-0.01486134619376014</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,13 +3868,13 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.008467537616080975</v>
+        <v>-0.002107024290768366</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08573627194078466</v>
+        <v>0.07496602947947231</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1125555440714856</v>
+        <v>-0.0214548695162985</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.04027991672288237</v>
+        <v>-0.00632712710524861</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01599000396456107</v>
+        <v>-0.00117070721410182</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,34 +3910,34 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.009952879077107506</v>
+        <v>-0.007549135844644841</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
         <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.001755178104207216</v>
+        <v>0.0007712236394845508</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.09216070965418269</v>
+        <v>-0.0189572848394598</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.03721760882705192</v>
+        <v>-0.01528826599130171</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.02134882430590351</v>
+        <v>-0.0007838771131267841</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03699649765902081</v>
+        <v>0.01774438744774259</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02641245564637097</v>
+        <v>-0.005348405262925932</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01298959220335065</v>
+        <v>-0.005235518858116479</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2894177295007844</v>
+        <v>0.1079348633565138</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1278633934681711</v>
+        <v>-0.007883111513852823</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,67 +4003,67 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.01575091226041233</v>
+        <v>0.0101358427155846</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0446945921101268</v>
+        <v>-0.01778659744157941</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1184155112994101</v>
+        <v>-0.01829461304747907</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.02678022058912093</v>
+        <v>-0.008985290159930326</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.002803734089909626</v>
+        <v>0.01080611636449299</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1302528654624796</v>
+        <v>0.04043469193177903</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.01548688122689996</v>
+        <v>0.013847612408169</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.05875066265152044</v>
+        <v>0.01852636594964902</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
@@ -4072,25 +4072,25 @@
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.003433895497042505</v>
+        <v>-0.0082832548426683</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.007213150153528406</v>
+        <v>-0.006758052323290461</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.04750460242046535</v>
+        <v>-0.02147604865794184</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.006433701622301368</v>
+        <v>0.005088681429042168</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.04310391540849617</v>
+        <v>0.01480247157130821</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.01152280828345264</v>
+        <v>-0.03336423318444996</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.03103730940761419</v>
+        <v>0.003631198475750958</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.009077321142871835</v>
+        <v>0.01804147409958723</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.04648359518432963</v>
+        <v>-0.0212879599674245</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,10 +4153,10 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.01361341444437383</v>
+        <v>0.003331933717878688</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
@@ -4165,22 +4165,22 @@
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.03427723579578522</v>
+        <v>0.01326461488513046</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1528491629053458</v>
+        <v>-0.02273131492083756</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.07594153930336882</v>
+        <v>-0.00672961061461189</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,97 +4189,97 @@
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.02054685652619925</v>
+        <v>-0.00964466005759183</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.002898659609278471</v>
+        <v>-0.010212729810446</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.02263601769193711</v>
+        <v>0.005366924111547859</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.02183285786109637</v>
+        <v>-0.02082289867069418</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.001914452699915123</v>
+        <v>0.009972633971029503</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01021015385862562</v>
+        <v>0.01291204643729888</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.02734884386570322</v>
+        <v>-0.009641170722792341</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.004487186699917747</v>
+        <v>-0.0265676290694668</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.04493754976007811</v>
+        <v>0.001519862151751812</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.05092790136057992</v>
+        <v>0.01005380204788298</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.08142634471582173</v>
+        <v>-0.006188134606532017</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.008810810578256806</v>
+        <v>0.01897319338777524</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.03334305503796309</v>
+        <v>0.002249428499958908</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.06335220925063867</v>
+        <v>-0.02679209743614397</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.004484470752788955</v>
+        <v>-0.001150571904613506</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,22 +4327,22 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.02036078383570714</v>
+        <v>0.01431121522998008</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.05917655950005488</v>
+        <v>-0.01390346032927481</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.004236033390694438</v>
+        <v>0.001789064130705913</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,16 +4351,16 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.05720346151607904</v>
+        <v>0.03783900568972479</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.07396768913160159</v>
+        <v>0.001597085542078211</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,25 +4369,25 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.05076202182965946</v>
+        <v>-0.01431850070043841</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.003870292290939853</v>
+        <v>0.0009576872868840309</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.08217069071957021</v>
+        <v>-0.005150918425054276</v>
       </c>
       <c r="GA7" t="n">
         <v>0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.04273870771218595</v>
+        <v>0.002064209495017468</v>
       </c>
     </row>
     <row r="8">
@@ -4985,16 +4985,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4938840515226859</v>
+        <v>0.1325437764644103</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.306079308279613</v>
+        <v>-0.1163565150630472</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.07808622780190388</v>
+        <v>-0.009152664239720665</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
         <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,19 +5012,19 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3706321382130284</v>
+        <v>0.1390557724238984</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3113953181656537</v>
+        <v>-0.1845790432961635</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1542648649536104</v>
+        <v>-0.03353232613311947</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
@@ -5036,19 +5036,19 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.04731013537627507</v>
+        <v>0.01053558402771886</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.02740356131096468</v>
+        <v>-0.01396103541287236</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.06894744165804371</v>
+        <v>-0.01974003008440905</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -5057,7 +5057,7 @@
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,22 +5066,22 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1510762384155205</v>
+        <v>0.001292741598100661</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01523680635315029</v>
+        <v>-0.04197588514035291</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.01189127296609297</v>
+        <v>-0.04928436243958054</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
@@ -5090,49 +5090,49 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.05478642153233355</v>
+        <v>0.05570127719287547</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.0512519864089678</v>
+        <v>-0.05973127292102211</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.09117058544445709</v>
+        <v>0.03012436342302433</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.6436056452959883</v>
+        <v>0.1564823707575459</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.07441402540351801</v>
+        <v>-0.06957707841117204</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1307172886369436</v>
+        <v>-0.1419907697118809</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5141,22 +5141,22 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.04306043450640847</v>
+        <v>-0.000167800519575402</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.1083713082039403</v>
+        <v>-0.001432859590790317</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.2238755070515737</v>
+        <v>0.0003855332796673055</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1394873754213819</v>
+        <v>0.01337219227322738</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.1211188029755046</v>
+        <v>0.005244956122343606</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1001398480182587</v>
+        <v>0.03422474996787929</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,19 +5201,19 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1141418120276387</v>
+        <v>0.04537753548331159</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0232155659848323</v>
+        <v>0.03166809053282883</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.02799039843353086</v>
+        <v>-0.01104332035754001</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5228,19 +5228,19 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1297297332143362</v>
+        <v>-0.06469692664198519</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0398894714901398</v>
+        <v>0.0849039664613392</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01640259928863805</v>
+        <v>0.01432097982482161</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ9" t="n">
         <v>-0</v>
@@ -5249,52 +5249,52 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.006421308790308207</v>
+        <v>-0.06556528698283347</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1893355248480227</v>
+        <v>0.197303069537214</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.09341611992064715</v>
+        <v>0.04696390103859248</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.108520422810106</v>
+        <v>-0.05531015645550022</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.07732180728961602</v>
+        <v>0.08697187347440771</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.007338470863742413</v>
+        <v>0.02056120078435577</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB9" t="n">
         <v>0</v>
@@ -5303,28 +5303,28 @@
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.00924184977443303</v>
+        <v>-0.0002950437324441652</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1235442363774332</v>
+        <v>0.01674162019008493</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03624166936153116</v>
+        <v>-0.04413298787209986</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5333,25 +5333,25 @@
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.1064681696410069</v>
+        <v>-0.07345468709785966</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.006470297685632571</v>
+        <v>0.06277003452937262</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.04040613265315553</v>
+        <v>0.0139947704595276</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,49 +5363,49 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.03613382926709811</v>
+        <v>-0.01427981682215387</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.004693924301401129</v>
+        <v>0.05523417904869284</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.06946503206760529</v>
+        <v>-0.01940968962947125</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.0483595827844716</v>
+        <v>-0.007324555818148651</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.04530496374779223</v>
+        <v>0.06210481809657922</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.04567043004622476</v>
+        <v>0.03595797962991704</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
@@ -5414,25 +5414,25 @@
         <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.1006342342662698</v>
+        <v>-0.05764836606805145</v>
       </c>
       <c r="EQ9" t="n">
         <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.07181275334616399</v>
+        <v>-0.05503182826466384</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.03023882554240447</v>
+        <v>0.01565534454142335</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,73 +5444,73 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.1048401492115635</v>
+        <v>-0.06652581564664835</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.06879820987390518</v>
+        <v>0.1047507510874277</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.0009166037269437713</v>
+        <v>0.0121842987859718</v>
       </c>
       <c r="FC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.03203769553957014</v>
+        <v>-0.0446811995312231</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.08053811320820298</v>
+        <v>0.01306950949018895</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.1000411496181689</v>
+        <v>-0.04190799937535342</v>
       </c>
       <c r="FL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.01236097989209494</v>
+        <v>0.0555813828477115</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.002019921276901681</v>
+        <v>0.1264259355672113</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.159415487083044</v>
+        <v>-0.04295190371434501</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
@@ -5525,13 +5525,13 @@
         <v>-0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.006833548934374979</v>
+        <v>-0.01599790942783372</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.009868061882926597</v>
+        <v>0.03915161947632292</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
@@ -5543,10 +5543,10 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7919503473135145</v>
+        <v>0.1684996779670657</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5851757249729903</v>
+        <v>-0.4183992368587304</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2974116344686988</v>
+        <v>-0.2488041227146982</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,61 +5572,61 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-8.381439017250536e-12</v>
+        <v>4.978108004033698e-11</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4545329312671721</v>
+        <v>0.07024033686392861</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5256344539786794</v>
+        <v>-0.6978071180900643</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3644070809065779</v>
+        <v>-0.4057498744100314</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.00376827229315548</v>
+        <v>0.01231702779782222</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1110915036939743</v>
+        <v>0.03694369035876902</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1078986167479008</v>
+        <v>-0.1289001088073067</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1641692645808584</v>
+        <v>-0.218126488081383</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.05576755393727881</v>
+        <v>0.0406599169039458</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -5635,106 +5635,106 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.110599702796036</v>
+        <v>-0.1109443117842367</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.046085715181809</v>
+        <v>0.05285389592646245</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.08300231357882573</v>
+        <v>-0.1783637616599201</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.04980973976234624</v>
+        <v>0.05651090741788591</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.04277807133789054</v>
+        <v>0.1542450870034117</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.1099722506989578</v>
+        <v>-0.07561570044175984</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.1369209336731763</v>
+        <v>-0.02322007927146212</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.01390012496808066</v>
+        <v>-0.01987348405809104</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.6820943308475239</v>
+        <v>0.2384757860600464</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.1713841442284597</v>
+        <v>0.01910305517284189</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.04039773424396099</v>
+        <v>-0.4895699634890738</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0494217452272702</v>
+        <v>-0.2054007543711521</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.03325804974323222</v>
+        <v>-0.06293922334594319</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.2288590238038364</v>
+        <v>-0.2397388197700187</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.5199521048030969</v>
+        <v>-0.1766798016756657</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI10" t="n">
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.02690821453259533</v>
+        <v>0.01584983622253057</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,52 +5743,52 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.4626020802441376</v>
+        <v>0.2203046359870593</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.272714532005333</v>
+        <v>0.2088912722720543</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1417556229384282</v>
+        <v>0.1079116918281421</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>-0.06605373927711605</v>
+        <v>0.08866868696126026</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU10" t="n">
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.4007363687902138</v>
+        <v>0.2670076180124046</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.05991095461027662</v>
+        <v>-0.1431694898509756</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.09751587371209894</v>
+        <v>-0.1356052307890606</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0.03465816790355555</v>
+        <v>-0.07840841965663224</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -5797,16 +5797,16 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.1661855085058949</v>
+        <v>0.002689689489930429</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.09083001200485187</v>
+        <v>0.1768812191328612</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.01828681484742251</v>
+        <v>0.1040872760017281</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5815,7 +5815,7 @@
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0.02013153161761387</v>
+        <v>-0.02411677519279294</v>
       </c>
       <c r="CL10" t="n">
         <v>0</v>
@@ -5824,43 +5824,43 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.1050501625222086</v>
+        <v>-0.06245272212943948</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.167702612860346</v>
+        <v>0.2583620879302658</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.03017921634921891</v>
+        <v>0.3658143634414878</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.117893638426664</v>
+        <v>0.1771379218938859</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1135451407866876</v>
+        <v>0.01300224057774019</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.170253363409792</v>
+        <v>0.218675972566909</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.008278402067674327</v>
+        <v>0.1399842521496245</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,61 +5869,61 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0.02319198033779078</v>
+        <v>-0.02391259641036314</v>
       </c>
       <c r="DD10" t="n">
         <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.1522369689014741</v>
+        <v>-0.005116932474184796</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.1381952043334875</v>
+        <v>0.08017472050228505</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.03117435136209187</v>
+        <v>0.02590481583769353</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.01495466721430776</v>
+        <v>-0.04702622632446771</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.1666304706927718</v>
+        <v>-0.07412264746042792</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.05332938081465131</v>
+        <v>0.1065518875694777</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01437878667581507</v>
+        <v>0.005560678155965485</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.2123895642308011</v>
+        <v>0.2271086104388494</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
@@ -5932,43 +5932,43 @@
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.02274933002614107</v>
+        <v>-0.06307502960026502</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.1184039698077381</v>
+        <v>0.07129062769320503</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0393951935255698</v>
+        <v>-0.1295493982905621</v>
       </c>
       <c r="EB10" t="n">
         <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.1465593866150426</v>
+        <v>0.1648911267326604</v>
       </c>
       <c r="EE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.03576568168195603</v>
+        <v>0.02250922579795163</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.07143257608362555</v>
+        <v>0.1426886753016797</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.1259781180091018</v>
+        <v>0.006566367478524147</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,7 +5977,7 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0.008639380143167459</v>
+        <v>-0.02175619184925935</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
@@ -5986,43 +5986,43 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.1782606048008105</v>
+        <v>-0.02559189389034311</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.1401205053203873</v>
+        <v>0.3050593992133055</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.06192802935690775</v>
+        <v>0.03756742718521153</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.2160383739274626</v>
+        <v>-0.003561145221387924</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.1124501122968305</v>
+        <v>-0.03659721680507558</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.1807724809288792</v>
+        <v>0.221244701929131</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.03932448566005945</v>
+        <v>0.1356152649237448</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6031,25 +6031,25 @@
         <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0.04574845213384448</v>
+        <v>-0.0272439240010811</v>
       </c>
       <c r="FF10" t="n">
         <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.09483844906842989</v>
+        <v>0.05238297701230329</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.1531106192523317</v>
+        <v>0.06582302450466648</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.05067503099857541</v>
+        <v>0.132254370471759</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
@@ -6058,61 +6058,61 @@
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.06637924586418319</v>
+        <v>-0.08323194062725216</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.1663356075744526</v>
+        <v>0.00382658439393547</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.05385061095423391</v>
+        <v>0.08794763462719322</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.05217943640571332</v>
+        <v>-0.03339379424139451</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
         <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.01124279350085143</v>
+        <v>-0.2101825487702873</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.001080539197334648</v>
+        <v>-0.008681675316583697</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.01209659214558685</v>
+        <v>0.05415118183513179</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.1486675330541789</v>
+        <v>-0.04631266147267381</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6123,25 +6123,25 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.191536961073633</v>
+        <v>0.6552406542839437</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1688970403129619</v>
+        <v>0.09964994335597013</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.09702173996738231</v>
+        <v>-0.5240343562369927</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1110758015721405</v>
+        <v>0.6872714583268739</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,16 +6159,16 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1717453940111781</v>
+        <v>-0.09188527662146774</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.109411862884896</v>
+        <v>-0.4828318553595638</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03964486448744649</v>
+        <v>0.1178103554532951</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,16 +6186,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.004478587255027498</v>
+        <v>-0.1104221869285574</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02812987884994596</v>
+        <v>-0.01240764022690088</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6204,19 +6204,19 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.05388456874900212</v>
+        <v>-0.1065288974570188</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0417745077848769</v>
+        <v>-0.4240293920360576</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02796746983933104</v>
+        <v>0.1456532106142846</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6225,13 +6225,13 @@
         <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.02956064504689443</v>
+        <v>0.1495109612523089</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,37 +6240,37 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.03412227866977988</v>
+        <v>0.002326219503569976</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.008817790888157977</v>
+        <v>-0.06720232354343116</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1903371702613423</v>
+        <v>0.5224655918943146</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.03900997029189399</v>
+        <v>-0.3169525293412913</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.01159978150438305</v>
+        <v>-0.08163292471332735</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -6279,13 +6279,13 @@
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03800252417809438</v>
+        <v>0.0385064736887599</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,52 +6294,52 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1362339946359772</v>
+        <v>-0.02707604561925208</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.07961817121283192</v>
+        <v>-0.2054895912214069</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1118977711934675</v>
+        <v>0.1494970472204904</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.08134023964616811</v>
+        <v>0.1944594015876628</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.04421103282378233</v>
+        <v>0.1859212977595249</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.09698831673116559</v>
+        <v>0.4663122695518951</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,97 +6348,97 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.02006734500059025</v>
+        <v>-0.05753099758889726</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.007132803704538893</v>
+        <v>-0.1645560805675785</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.03674906126562523</v>
+        <v>-0.2252461840317455</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0221892710897563</v>
+        <v>-0.06054560555266499</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.03355128165065102</v>
+        <v>0.199864110087603</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.05991958079345149</v>
+        <v>-0.2624452328566106</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.04745174578989007</v>
+        <v>0.1591813258189712</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.01104098113218662</v>
+        <v>0.05194542411834999</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU11" t="n">
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.01701984695262159</v>
+        <v>-0.1903902536331013</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01967378466858445</v>
+        <v>-0.04489181429873645</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.03234132967958985</v>
+        <v>0.2105960957434513</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.02358948426291502</v>
+        <v>-0.2124031820222009</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,37 +6456,37 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01800599890940369</v>
+        <v>-0.2438823250597195</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01168101391560045</v>
+        <v>0.03226766411164628</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.02067718917928562</v>
+        <v>-0.1355105504044116</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01172251614530922</v>
+        <v>-0.04065855000175175</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.04245393296424246</v>
+        <v>-0.02047695690306423</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6501,142 +6501,142 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.0006749985424348048</v>
+        <v>-0.01080581267606824</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.04600691837066276</v>
+        <v>0.06414478171542595</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.01688992198607604</v>
+        <v>0.136144272669146</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.004100104207253312</v>
+        <v>-0.03551372020390734</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01329626521445822</v>
+        <v>-0.1407541785734811</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.006687376457588327</v>
+        <v>0.1630672056994416</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01811188055615685</v>
+        <v>-0.1414806590448166</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.005941546084627517</v>
+        <v>-0.2329192729204914</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.03852549268115732</v>
+        <v>0.1266306729598368</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.01796571760883878</v>
+        <v>-0.2461110390669858</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.02405463391126945</v>
+        <v>-0.09504278653622024</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.03773295818752459</v>
+        <v>0.1620674933658102</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.0421247951002553</v>
+        <v>-0.2377743213380181</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.03699707652167864</v>
+        <v>0.2034885929201912</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03475304794284123</v>
+        <v>0.1387561405898837</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.01545676123534834</v>
+        <v>0.1566436577061641</v>
       </c>
       <c r="FR11" t="n">
         <v>0</v>
@@ -6645,43 +6645,43 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.002329389394907541</v>
+        <v>0.04901929499876802</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.02322055298535955</v>
+        <v>0.03142278276462815</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.06100562909636191</v>
+        <v>-0.1156899094870616</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC11" t="n">
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.00179393364764116</v>
+        <v>0.2047983669366232</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG11" t="n">
         <v>0</v>
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>1.015721109194186</v>
+        <v>0.8449608315093541</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.892237273332481</v>
+        <v>-0.5669036103134258</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04374953837106749</v>
+        <v>-0.1335537472750538</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6719,16 +6719,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7022891664270824</v>
+        <v>0.7621551729403327</v>
       </c>
       <c r="L12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8339498223831219</v>
+        <v>-0.7751108450828977</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1743021203393633</v>
+        <v>-0.280527378276351</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6737,7 +6737,7 @@
         <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -6746,49 +6746,49 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1272941699102658</v>
+        <v>0.1198679343607357</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1549165439884053</v>
+        <v>-0.0923923541310992</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1506190585838759</v>
+        <v>-0.1343601177338872</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1566268767985497</v>
+        <v>-0.0534625869711421</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.03349251053674615</v>
+        <v>-0.2490212591216084</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.05115518316166977</v>
+        <v>-0.2620006639071347</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6797,19 +6797,19 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.1272735010221328</v>
+        <v>0.2593127342278534</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.08473214618842981</v>
+        <v>-0.1820871553258228</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.08934659968056101</v>
+        <v>0.06991219687708704</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6827,43 +6827,43 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.7049441738522846</v>
+        <v>0.4951656875613545</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.276795961425541</v>
+        <v>-0.1802792336219703</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1007331378757272</v>
+        <v>-0.3410368105900862</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1525244614143077</v>
+        <v>0.09105426764641344</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.3031088943809816</v>
+        <v>-0.1788863926050716</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.2887815011978827</v>
+        <v>0.0007610007458444482</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,25 +6881,25 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.220948902879664</v>
+        <v>-0.008651083993503903</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.07732164236832455</v>
+        <v>0.0822327266934927</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1393452778622005</v>
+        <v>0.210389202218061</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
         <v>-0</v>
@@ -6908,22 +6908,22 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.4179426014275878</v>
+        <v>0.4288900952014765</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.1750261038753706</v>
+        <v>-0.1747151107836311</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.007867571275405881</v>
+        <v>-0.08140530128441413</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
         <v>0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1907684205015877</v>
+        <v>-0.2846126403714879</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.1453452979331813</v>
+        <v>0.2608577724169912</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.05217098860370653</v>
+        <v>0.04661067404174905</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6956,49 +6956,49 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.03964299278957414</v>
+        <v>-0.2775296121921719</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.1677816557540052</v>
+        <v>0.4693176529479311</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.07139141257055144</v>
+        <v>0.1342957761256225</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1612553450375413</v>
+        <v>-0.2542438434896669</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.1811516088750526</v>
+        <v>0.2578544554935577</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.02708360894718725</v>
+        <v>0.09100608345948014</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7010,31 +7010,31 @@
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.1079903645463838</v>
+        <v>-0.1776621525450726</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.1209641756899011</v>
+        <v>0.05119337651865891</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1269808839662449</v>
+        <v>-0.08909556095609689</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM12" t="n">
         <v>0</v>
@@ -7043,19 +7043,19 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.1001339192703101</v>
+        <v>-0.1958320994251386</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.1388426023333306</v>
+        <v>0.08906522297297807</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.08633517765447156</v>
+        <v>0.00364158274966511</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
@@ -7070,76 +7070,76 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.007737698071876485</v>
+        <v>0.01187668586170531</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.002326654632151751</v>
+        <v>-0.1507561437637881</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.04604131621648218</v>
+        <v>0.04831227289628852</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.08533243378125324</v>
+        <v>-0.1763030690643742</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.1011231185167572</v>
+        <v>0.2297962067770016</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.03411431179549142</v>
+        <v>0.1028934392482932</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.1452456616776548</v>
+        <v>-0.2048694940865249</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.1449313260459559</v>
+        <v>0.1707472752517706</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.01401330030732104</v>
+        <v>-0.004019215211182348</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,49 +7151,49 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1621387283756862</v>
+        <v>-0.3122661817859475</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.1843893842615595</v>
+        <v>0.289874193928276</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.01955141911115492</v>
+        <v>0.03295809394320103</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.08262646252445886</v>
+        <v>-0.1581741551104092</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.1011827543571812</v>
+        <v>0.1189234214190974</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.05736098675700841</v>
+        <v>0.06391185211444207</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
@@ -7205,52 +7205,52 @@
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.002587443898373514</v>
+        <v>0.1426840547555596</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.0002031920811136562</v>
+        <v>0.2282997452027667</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.1671486071765743</v>
+        <v>0.07307460292675179</v>
       </c>
       <c r="FU12" t="n">
         <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.03724161077132321</v>
+        <v>-0.1995300762353893</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.04282071490424864</v>
+        <v>0.1415307623962894</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>-0</v>
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.497779385989518</v>
+        <v>0.5760474750369057</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1198440719462276</v>
+        <v>0.1671753688979462</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4049268109924137</v>
+        <v>-0.6471765324838457</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7285,22 +7285,22 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3845487104880416</v>
+        <v>0.7209899225819746</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.08117931863762878</v>
+        <v>0.006541452337922818</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4205863774527087</v>
+        <v>-0.6295475668028719</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -7312,10 +7312,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04346610209853723</v>
+        <v>0.2150225352210618</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7324,13 +7324,13 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.07323356467313184</v>
+        <v>-0.3827014462302239</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.01285185369048701</v>
+        <v>-0.09658792408999432</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -7342,22 +7342,22 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0823024210561398</v>
+        <v>0.001032817960855532</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.06949833622873573</v>
+        <v>-0.6526097880737217</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.0344648476467973</v>
+        <v>-0.3191216522953093</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0670973471923552</v>
+        <v>0.2123782038029217</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.02104806969331902</v>
+        <v>0.04863935557407559</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.04835430349897542</v>
+        <v>-0.1462455540701228</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7396,7 +7396,7 @@
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.300929395833234</v>
+        <v>0.8973543755155444</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,10 +7405,10 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.05388210816142656</v>
+        <v>-0.1313823415438855</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.14604897173511</v>
+        <v>-0.1457358123037489</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -7417,55 +7417,55 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1339162985089785</v>
+        <v>-0.2855822093248186</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1116647941279855</v>
+        <v>-0.3948336072156474</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.1110968994782579</v>
+        <v>-0.4631213240123568</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1156837112888523</v>
+        <v>0.0486456718292194</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.03954302662468592</v>
+        <v>0.0522126749621763</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0.008921067683036755</v>
+        <v>0.1205493643605481</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1808656713140172</v>
+        <v>0.5457127473823842</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,64 +7486,64 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.07093834898639033</v>
+        <v>-0.2245458938882871</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.1643237898242703</v>
+        <v>-0.4234676513245614</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.08869005318504716</v>
+        <v>-0.2186628017948613</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01135090798467217</v>
+        <v>0.02187188461976671</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.08944266162078773</v>
+        <v>0.2646108381621266</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.03507918930830194</v>
+        <v>-0.5071937717863721</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01446959435506859</v>
+        <v>0.8495630793556667</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.0006226635375430843</v>
+        <v>0.5180521679904556</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7555,55 +7555,55 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.07157294928568596</v>
+        <v>-0.1970958827788012</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.003148031649138679</v>
+        <v>-0.00813185193039837</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.09519301362834437</v>
+        <v>0.2359153042412024</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.02525519466005381</v>
+        <v>-0.03144695728448629</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.04288009001324275</v>
+        <v>-0.2199797156680058</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.009888034936216438</v>
+        <v>0.0223181441349806</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
@@ -7612,25 +7612,25 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.03511972846573112</v>
+        <v>-0.08684293542681361</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.007561685306060763</v>
+        <v>-0.02329640690167227</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.028329500196668</v>
+        <v>0.2701468015940337</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
@@ -7639,22 +7639,22 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.003363345465448496</v>
+        <v>0.08070670285101443</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.03273012990805303</v>
+        <v>-0.02730223713385516</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.02522836886434937</v>
+        <v>0.2092417923503717</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>-0</v>
@@ -7663,22 +7663,22 @@
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.05075373572746175</v>
+        <v>-0.05176976906723595</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0341729360628447</v>
+        <v>-0.1508742889999227</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.08854742305821749</v>
+        <v>0.04056982545174961</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
@@ -7693,22 +7693,22 @@
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.03796107526737234</v>
+        <v>-0.01285955649789999</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01910474023441656</v>
+        <v>-0.03386691705216312</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.03825849477726069</v>
+        <v>0.1962876584485511</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7717,55 +7717,55 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.0682802758583739</v>
+        <v>-0.2329273624408741</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.00263019077419847</v>
+        <v>-0.01253824169986596</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.08225404582740879</v>
+        <v>0.2424089166754911</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.06211666018879413</v>
+        <v>-0.3362062246610129</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.004777410118173496</v>
+        <v>0.09908313327766871</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.07992660211626615</v>
+        <v>0.07239483839020902</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,7 +7774,7 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01197084865238169</v>
+        <v>0.1148391155514469</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,10 +7783,10 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.05541567777723524</v>
+        <v>0.2602149983581425</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.01412931890546239</v>
+        <v>-0.04535947404024876</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,25 +7795,25 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.005867686727836091</v>
+        <v>-0.1080917788571736</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.01057933167715532</v>
+        <v>0.1134536771505018</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,105 +7822,105 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.919787561870037</v>
+        <v>0.7883176562869406</v>
       </c>
       <c r="C14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.567785434273558</v>
+        <v>-0.553324994003875</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2465478488937902</v>
+        <v>-0.187285083589425</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5531625021754369</v>
+        <v>0.6973020229046173</v>
       </c>
       <c r="L14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5047717241440181</v>
+        <v>-0.7113928063277839</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2027342868320409</v>
+        <v>-0.262917503962272</v>
       </c>
       <c r="O14" t="n">
         <v>-0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1467597845651084</v>
+        <v>0.1032823863109785</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1375662976205441</v>
+        <v>-0.108313872235689</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1431926405875698</v>
+        <v>-0.06405996940552763</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
         <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.03266861101025852</v>
+        <v>-0.06708919777610738</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.09121927969937434</v>
+        <v>-0.1174384590418143</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.07005039988467772</v>
+        <v>-0.03518553633875046</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
@@ -7932,52 +7932,52 @@
         <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.1132524961793543</v>
+        <v>0.2498363962533288</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.06622620156763595</v>
+        <v>-0.09972033953524859</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.05144010558343668</v>
+        <v>0.1647493792302062</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0.6483019697330249</v>
+        <v>0.5726192832631772</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.06059126284957176</v>
+        <v>-0.1627457687348933</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.05599510798052873</v>
+        <v>-0.1837214189746768</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -7992,19 +7992,19 @@
         <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0.09508697909372185</v>
+        <v>-0.006482154292232206</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.3020417654789765</v>
+        <v>-0.1704728838147439</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.3728319180977822</v>
+        <v>-0.1920500693040453</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI14" t="n">
         <v>-0</v>
@@ -8013,22 +8013,22 @@
         <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0.09437975706035014</v>
+        <v>-0.1249586616507952</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.01303384372951269</v>
+        <v>0.06235545027853261</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.07146454100286709</v>
+        <v>0.06320565748982684</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
@@ -8043,82 +8043,82 @@
         <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0.4036916742467141</v>
+        <v>0.4456941718547833</v>
       </c>
       <c r="BW14" t="n">
         <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.04736905127651997</v>
+        <v>-0.2111342721631428</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0620491274869531</v>
+        <v>-0.02670765271183037</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.1845025206105687</v>
+        <v>-0.3197056354926123</v>
       </c>
       <c r="CF14" t="n">
         <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.1153389015858952</v>
+        <v>0.1999343908383414</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.02438633416077397</v>
+        <v>0.02866367026828189</v>
       </c>
       <c r="CI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
         <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.1204518092520713</v>
+        <v>-0.3161428283139197</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.02558039953487151</v>
+        <v>0.3628858726130459</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.02888754423439874</v>
+        <v>0.1436289218591545</v>
       </c>
       <c r="CR14" t="n">
         <v>-0</v>
       </c>
       <c r="CS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
@@ -8127,97 +8127,97 @@
         <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.157355884864487</v>
+        <v>-0.3150878377592945</v>
       </c>
       <c r="CX14" t="n">
         <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.1425893902983156</v>
+        <v>0.2030712645286336</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0216212329921873</v>
+        <v>0.04771596091105351</v>
       </c>
       <c r="DA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
         <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.01547739542413929</v>
+        <v>0.008934913513840754</v>
       </c>
       <c r="DG14" t="n">
         <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.09987467667197544</v>
+        <v>0.03820369293543109</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.09464237580731222</v>
+        <v>-0.05679452740856213</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.1278326963527882</v>
+        <v>-0.1757729131498621</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.1198143473792805</v>
+        <v>-0.06772886441973353</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.05352548274236195</v>
+        <v>-0.02620823490967186</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU14" t="n">
         <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.04506331138909341</v>
+        <v>0.1232690926205284</v>
       </c>
       <c r="DY14" t="n">
         <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.05888977047894089</v>
+        <v>0.1015966976724922</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.05957371232124359</v>
+        <v>0.01637739543469841</v>
       </c>
       <c r="EB14" t="n">
         <v>-0</v>
@@ -8226,28 +8226,28 @@
         <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
         <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.1317998902685211</v>
+        <v>-0.2739445011508023</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.01056912057368386</v>
+        <v>0.1475931306084656</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.04341283953067725</v>
+        <v>0.1157284645242327</v>
       </c>
       <c r="EK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL14" t="n">
         <v>0</v>
@@ -8262,16 +8262,16 @@
         <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.004472308604807225</v>
+        <v>-0.1994476988510383</v>
       </c>
       <c r="EQ14" t="n">
         <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.1108891855270511</v>
+        <v>0.1773457967764449</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02418454647676114</v>
+        <v>0.03404351081308097</v>
       </c>
       <c r="ET14" t="n">
         <v>0</v>
@@ -8280,141 +8280,141 @@
         <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.1516051946396716</v>
+        <v>-0.350713896400047</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.1226055225635541</v>
+        <v>0.2398300210702004</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.01844319590958707</v>
+        <v>0.02450001628572028</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
         <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.1139194920443419</v>
+        <v>-0.1364393597639689</v>
       </c>
       <c r="FI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>-0.0359190720919724</v>
+        <v>0.1306088649239897</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.02586706666098142</v>
+        <v>-0.02699794942896987</v>
       </c>
       <c r="FL14" t="n">
         <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
         <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.009544962595645703</v>
+        <v>0.04729112540781872</v>
       </c>
       <c r="FR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.01474121597773014</v>
+        <v>0.1706373593959226</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.02213597415766876</v>
+        <v>-0.008391691404085239</v>
       </c>
       <c r="FU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
         <v>-0</v>
       </c>
       <c r="FX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
         <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.02660860378190651</v>
+        <v>-0.2658820079306785</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.06365351474748922</v>
+        <v>0.1271165858884789</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
         <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
         <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.8655964687292396</v>
+        <v>-0.4340411249439008</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5931101341453784</v>
+        <v>0.2667016189708787</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1823255773249941</v>
+        <v>0.07798324917178222</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -8423,22 +8423,22 @@
         <v>-0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6945052853738087</v>
+        <v>-0.3858855724270199</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5250118876950072</v>
+        <v>0.3781920234069401</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1831319915815755</v>
+        <v>0.07686861913140322</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -8447,49 +8447,49 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1900700247229571</v>
+        <v>-0.05514804249388735</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.007026065615805555</v>
+        <v>0.06010671250931068</v>
       </c>
       <c r="W15" t="n">
-        <v>0.09138213169523338</v>
+        <v>-0.006436685216412433</v>
       </c>
       <c r="X15" t="n">
         <v>-0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1874493422047576</v>
+        <v>-0.02151658493073206</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.04662181351440424</v>
+        <v>0.1295571117295108</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.01354423417883386</v>
+        <v>-0.05654423689047454</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -8501,28 +8501,28 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.06491190018744647</v>
+        <v>-0.1901882256984314</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.1176680432499319</v>
+        <v>0.06211972270700226</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.1100532535589337</v>
+        <v>-0.2291122828923098</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -8531,22 +8531,22 @@
         <v>-0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.4372483075682472</v>
+        <v>-0.415569177970299</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.2262900607648971</v>
+        <v>0.1779216950274537</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1531879955578139</v>
+        <v>-0.02644162176769293</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
         <v>-0</v>
@@ -8558,25 +8558,25 @@
         <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.2352173034129204</v>
+        <v>0.06377378145403317</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.1649584945421389</v>
+        <v>0.0307603280471237</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.2703074954221892</v>
+        <v>0.1704905021797179</v>
       </c>
       <c r="BH15" t="n">
         <v>-0</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ15" t="n">
         <v>0</v>
@@ -8585,73 +8585,73 @@
         <v>-0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.1846277258457618</v>
+        <v>0.0824577771801123</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.05792677643834442</v>
+        <v>0.01302455409791513</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.197015301023118</v>
+        <v>0.03282593229934885</v>
       </c>
       <c r="BQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.188008397708503</v>
+        <v>-0.2907721744797679</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0.06889349691586451</v>
+        <v>0.1198062695280303</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.08934452889082937</v>
+        <v>-0.01869571239153123</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
       </c>
       <c r="CA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="n">
         <v>-0</v>
       </c>
       <c r="CC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.1315507700505086</v>
+        <v>0.2285115323800079</v>
       </c>
       <c r="CF15" t="n">
         <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.08576827611692256</v>
+        <v>-0.07889853220504331</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.006525858079906078</v>
+        <v>-0.006884176645957339</v>
       </c>
       <c r="CI15" t="n">
         <v>0</v>
@@ -8660,34 +8660,34 @@
         <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
       </c>
       <c r="CM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.08559320320133311</v>
+        <v>0.2752411165387268</v>
       </c>
       <c r="CO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.2006830141204715</v>
+        <v>-0.1132918799386886</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.213914605952655</v>
+        <v>-0.1619245312141702</v>
       </c>
       <c r="CR15" t="n">
         <v>0</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
         <v>0</v>
@@ -8696,16 +8696,16 @@
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.1293191642329138</v>
+        <v>0.2314446325173747</v>
       </c>
       <c r="CX15" t="n">
         <v>-0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.1185047858553469</v>
+        <v>-0.09910895319231665</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.01291795710434554</v>
+        <v>-0.01216490083672906</v>
       </c>
       <c r="DA15" t="n">
         <v>-0</v>
@@ -8720,28 +8720,28 @@
         <v>-0</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.1119374014447026</v>
+        <v>0.0385598828113477</v>
       </c>
       <c r="DG15" t="n">
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.148556836259942</v>
+        <v>-0.005223906405142866</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.01793995874979248</v>
+        <v>-0.0007594397961093</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
       </c>
       <c r="DL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM15" t="n">
         <v>0</v>
@@ -8750,25 +8750,25 @@
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.009467023837987722</v>
+        <v>0.1188700546611173</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.1920830032007415</v>
+        <v>-0.007956733254568856</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.02009635908399306</v>
+        <v>0.02892423021676517</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
@@ -8777,16 +8777,16 @@
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.07606119130654783</v>
+        <v>-0.04289524988243797</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.09151276342076632</v>
+        <v>0.01462476545148485</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.03013834287359566</v>
+        <v>-0.03475761007958232</v>
       </c>
       <c r="EB15" t="n">
         <v>0</v>
@@ -8798,76 +8798,76 @@
         <v>-0</v>
       </c>
       <c r="EE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF15" t="n">
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.1637407322840769</v>
+        <v>0.2317286022060314</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.1971854298013399</v>
+        <v>-0.07650569221622777</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.05999189328421383</v>
+        <v>-0.03027940361707557</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO15" t="n">
         <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.1608031973861739</v>
+        <v>0.1499596052206319</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.08655715125622312</v>
+        <v>-0.07511370798584928</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.112874690672338</v>
+        <v>-0.1069236859269757</v>
       </c>
       <c r="ET15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU15" t="n">
         <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.1269056943637601</v>
+        <v>0.2700527301296959</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.1002335234667717</v>
+        <v>-0.0918734582006745</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.009495510022802857</v>
+        <v>-0.01017979136494109</v>
       </c>
       <c r="FC15" t="n">
         <v>0</v>
@@ -8885,22 +8885,22 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.04004688739454586</v>
+        <v>0.1223667979273396</v>
       </c>
       <c r="FI15" t="n">
         <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.1536217167010182</v>
+        <v>-0.09243727311883962</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.114374688449322</v>
+        <v>0.06666588893789524</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
       </c>
       <c r="FM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN15" t="n">
         <v>0</v>
@@ -8912,19 +8912,19 @@
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.07149785004511366</v>
+        <v>0.02530268191411396</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0.008904147371079522</v>
+        <v>-0.008487743412618131</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.03578073600728576</v>
+        <v>-0.004151280736488382</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV15" t="n">
         <v>-0</v>
@@ -8933,19 +8933,19 @@
         <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
         <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.1199145827159166</v>
+        <v>0.1532571642313956</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.1025370758736707</v>
+        <v>-0.04018658956708536</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
@@ -8954,141 +8954,141 @@
         <v>-0</v>
       </c>
       <c r="GE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF15" t="n">
         <v>0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.2848951979924877</v>
+        <v>-0</v>
       </c>
       <c r="C16" t="n">
-        <v>-0</v>
+        <v>-0.2663970516101049</v>
       </c>
       <c r="D16" t="n">
-        <v>-0</v>
+        <v>0.219862594242654</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06515554111665034</v>
+        <v>-0.08059425265053838</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6463832384790541</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.313123735549621</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0</v>
+        <v>-0.2110806308633375</v>
       </c>
       <c r="M16" t="n">
-        <v>-0</v>
+        <v>0.143253398051119</v>
       </c>
       <c r="N16" t="n">
-        <v>0.008557643899974482</v>
+        <v>0.05308126729186962</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4565695353674425</v>
+        <v>-0</v>
       </c>
       <c r="P16" t="n">
         <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.007925637936257765</v>
+        <v>-0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.09735184129884901</v>
       </c>
       <c r="V16" t="n">
-        <v>-0</v>
+        <v>0.2361396921827598</v>
       </c>
       <c r="W16" t="n">
-        <v>0.07071612360969246</v>
+        <v>0.1150268794517982</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03850943167069237</v>
+        <v>-0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.1003507617645784</v>
+        <v>-0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>0.01659896635229007</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>-0.296539746179056</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.05694712116898171</v>
+        <v>-0.2637263277900881</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.006994091448976174</v>
+        <v>-0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.02066327015051685</v>
+        <v>-0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>-0.1575802095326843</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>0.1997835907191182</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.0442984785123487</v>
+        <v>0.09854129549877444</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.1681834195972504</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
         <v>-0</v>
@@ -9097,31 +9097,31 @@
         <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0.2234024227129534</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>-0.4353074465565159</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0</v>
+        <v>0.4467645726404236</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.04183134235004232</v>
+        <v>-0.2039279892799338</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.3916828114759273</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
         <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
@@ -9130,19 +9130,19 @@
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>-0.0984436479953229</v>
+        <v>-0</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0</v>
+        <v>0.02375009136701224</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0</v>
+        <v>-0.5495212737833163</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.09457443617312669</v>
+        <v>-0.1632255773280493</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.1017749003039087</v>
+        <v>-0</v>
       </c>
       <c r="BI16" t="n">
         <v>0</v>
@@ -9151,25 +9151,25 @@
         <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0.1198736400706679</v>
+        <v>-0</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>0.1137733414097837</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0</v>
+        <v>-0.01050131656966082</v>
       </c>
       <c r="BP16" t="n">
-        <v>-0.0550586649211712</v>
+        <v>0.212603562719351</v>
       </c>
       <c r="BQ16" t="n">
-        <v>-0.01194197170198105</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
         <v>0</v>
@@ -9181,22 +9181,22 @@
         <v>-0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>-0.09815731219264716</v>
+        <v>-0</v>
       </c>
       <c r="BW16" t="n">
-        <v>-0</v>
+        <v>-0.2210056288262256</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>0.670904540360734</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.01318265240407661</v>
+        <v>0.0161228064226668</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.1464543100264875</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9205,106 +9205,106 @@
         <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.08551665890684383</v>
+        <v>0</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>0.150953812020817</v>
       </c>
       <c r="CG16" t="n">
-        <v>0</v>
+        <v>-0.06582053725431392</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.01139498738448226</v>
+        <v>0.008672263314030822</v>
       </c>
       <c r="CI16" t="n">
-        <v>-0.0850937159536215</v>
+        <v>0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.01357352713627362</v>
+        <v>0</v>
       </c>
       <c r="CO16" t="n">
-        <v>-0</v>
+        <v>0.06178455644632756</v>
       </c>
       <c r="CP16" t="n">
-        <v>0</v>
+        <v>0.03095042710776032</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.0566070995155817</v>
+        <v>0.1307868046759903</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.1162579159936121</v>
+        <v>0</v>
       </c>
       <c r="CS16" t="n">
         <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.08305499554465062</v>
+        <v>-0</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0.1204247923337179</v>
       </c>
       <c r="CY16" t="n">
-        <v>-0</v>
+        <v>-0.06415097379952642</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.007976685762771298</v>
+        <v>0.03852244118618839</v>
       </c>
       <c r="DA16" t="n">
-        <v>-0.1107804797428832</v>
+        <v>0</v>
       </c>
       <c r="DB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.05215353303153252</v>
+        <v>-0</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>0.06865239345536918</v>
       </c>
       <c r="DH16" t="n">
-        <v>0</v>
+        <v>-0.1372807168360658</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.09655642833766886</v>
+        <v>-0.02677527764669843</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.002163861859805309</v>
+        <v>-0</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
@@ -9319,46 +9319,46 @@
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.03006978886838074</v>
+        <v>0</v>
       </c>
       <c r="DP16" t="n">
-        <v>-0</v>
+        <v>-0.02398639589825555</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>-0.08138650635476145</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.1298701413297423</v>
+        <v>0.1656097215028356</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.07474253176947639</v>
+        <v>-0</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.1075040433515474</v>
+        <v>-0</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>0.01689665771434515</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0</v>
+        <v>-0.0185336096599359</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.007588832239698224</v>
+        <v>-0.1776584928558029</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0.007860134943109904</v>
+        <v>-0</v>
       </c>
       <c r="EC16" t="n">
         <v>0</v>
@@ -9367,28 +9367,28 @@
         <v>-0</v>
       </c>
       <c r="EE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF16" t="n">
         <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.04815021449190214</v>
+        <v>0</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>0.07823719728036634</v>
       </c>
       <c r="EI16" t="n">
-        <v>-0</v>
+        <v>0.1032103323957011</v>
       </c>
       <c r="EJ16" t="n">
-        <v>-0.03324933141136681</v>
+        <v>-0.1058449467201291</v>
       </c>
       <c r="EK16" t="n">
-        <v>-0.05279717653273564</v>
+        <v>0</v>
       </c>
       <c r="EL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM16" t="n">
         <v>0</v>
@@ -9400,76 +9400,76 @@
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.1372646622677588</v>
+        <v>0</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>0.0326403386838509</v>
       </c>
       <c r="ER16" t="n">
-        <v>0</v>
+        <v>-0.1183556035001071</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.06666100796109349</v>
+        <v>-0.04088227377105128</v>
       </c>
       <c r="ET16" t="n">
-        <v>-0.02478110566837071</v>
+        <v>-0</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>-0</v>
       </c>
       <c r="EW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.08474829459449502</v>
+        <v>0</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>0.1374237401353703</v>
       </c>
       <c r="FA16" t="n">
-        <v>0</v>
+        <v>-0.1109856916813074</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.003446103159749068</v>
+        <v>0.02046725387460329</v>
       </c>
       <c r="FC16" t="n">
-        <v>-0.1034503628765184</v>
+        <v>-0</v>
       </c>
       <c r="FD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE16" t="n">
         <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.007671750747920411</v>
+        <v>0</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0.3082214634427982</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0</v>
+        <v>-0.1617745057866167</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.02803525051996195</v>
+        <v>-0.2591266956362787</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0.1168208623009953</v>
+        <v>0</v>
       </c>
       <c r="FM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN16" t="n">
         <v>-0</v>
@@ -9478,58 +9478,1765 @@
         <v>0</v>
       </c>
       <c r="FP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.01960187301061707</v>
+        <v>-0</v>
       </c>
       <c r="FR16" t="n">
-        <v>0</v>
+        <v>0.007044099716559353</v>
       </c>
       <c r="FS16" t="n">
-        <v>0</v>
+        <v>0.01734089210601025</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.04441956389729004</v>
+        <v>0.2464263675778678</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0.1436406594752059</v>
+        <v>0</v>
       </c>
       <c r="FV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW16" t="n">
         <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.0482915911799106</v>
+        <v>-0</v>
       </c>
       <c r="GA16" t="n">
-        <v>0</v>
+        <v>0.1393557049563471</v>
       </c>
       <c r="GB16" t="n">
-        <v>0</v>
+        <v>-0.102679653059855</v>
       </c>
       <c r="GC16" t="n">
         <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.07346558152105309</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
         <v>0</v>
       </c>
       <c r="GG16" t="n">
         <v>-0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.4997772045611953</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.1160568986501918</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6152904566212725</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.6534324835292215</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3545299798571633</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.6144429665845593</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.1123539648629018</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1907164193140526</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.07845715880202443</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.009979453685685681</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.3195564908803534</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.1668842850947195</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.1565977223625222</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-0.04257892733016525</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.1378946697056548</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-0.9293956002300401</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.1383152052211439</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.360156396131434</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.07108861219645074</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.2062672374423699</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.1561978219182692</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-0.139740634684742</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.1971819999332158</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-0.01974027056924131</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-0.3058405981329478</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0.09761449364575644</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0.2125242114021156</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.1890813212030383</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>-0.03211555990660853</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>-0.1683021678671686</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0.3892342059943018</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>-0.1521883984214743</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>-0.1446915864998343</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>0.1451530877964388</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>-0.02994904381377683</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>-0.1849086695613993</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>0.1347386316943949</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.2049009666283546</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>-0.05033323285704659</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>-0.001117067857539157</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>0.07641790113847217</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>-0.05991856046019378</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>-0.1490758353977962</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>-0.03464125013052168</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>-0.1426976518034697</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>0.0300440503535191</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>0.01349521644200579</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>-0.07950916115586538</v>
+      </c>
+      <c r="EL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP18" t="n">
+        <v>0.07597720850083126</v>
+      </c>
+      <c r="EQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES18" t="n">
+        <v>0.05598540873848382</v>
+      </c>
+      <c r="ET18" t="n">
+        <v>-0.2256872675365518</v>
+      </c>
+      <c r="EU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY18" t="n">
+        <v>0.2166362683927181</v>
+      </c>
+      <c r="EZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB18" t="n">
+        <v>0.004198924531407021</v>
+      </c>
+      <c r="FC18" t="n">
+        <v>-0.1726415781338476</v>
+      </c>
+      <c r="FD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH18" t="n">
+        <v>0.1897651243875684</v>
+      </c>
+      <c r="FI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK18" t="n">
+        <v>-0.1441172209582797</v>
+      </c>
+      <c r="FL18" t="n">
+        <v>-0.1231061536372638</v>
+      </c>
+      <c r="FM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ18" t="n">
+        <v>-0.01155203238041576</v>
+      </c>
+      <c r="FR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT18" t="n">
+        <v>0.02267974634036901</v>
+      </c>
+      <c r="FU18" t="n">
+        <v>-0.05860305159617176</v>
+      </c>
+      <c r="FV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ18" t="n">
+        <v>0.05222768365664097</v>
+      </c>
+      <c r="GA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD18" t="n">
+        <v>-0.02629149779586409</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG18" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.195157894278973</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.03010566203598728</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3228709442963339</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.2282267087947311</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.1706932609916142</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.3147669968581507</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.06662961444953992</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.03292705953001026</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.05094651526772385</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.03825351466016787</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.1317974553261275</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.0387778791172097</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.05931053562323299</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-0.1126032494002733</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.1418044365512839</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-0.3502687298855605</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.0327459936892594</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.2238123594117792</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0.1730592958968201</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0.1429409991384474</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0.01262054472577528</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-0.03199208889296787</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-0.0675237343865097</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>-0.01976781813820655</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>-0.2029366279650036</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0.03109386044473095</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0.183041892922131</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0.1138202018940217</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>-0.03883300886679578</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>-0.07635187296563897</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0.05634316356306052</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>-0.155811391258451</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>-0.06820774365026713</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>0.111096460458607</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>-0.05709683421600811</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>-0.08981382927438107</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>0.01231375245355818</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>0.03453911376597287</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>-0.05672374427592718</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>0.05603496424699197</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>-0.06947972416022732</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>-0.08575950734994953</v>
+      </c>
+      <c r="DT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX19" t="n">
+        <v>0.07016152764088668</v>
+      </c>
+      <c r="DY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA19" t="n">
+        <v>-0.02273510897835573</v>
+      </c>
+      <c r="EB19" t="n">
+        <v>0.05984377867833878</v>
+      </c>
+      <c r="EC19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG19" t="n">
+        <v>0.07829290341981954</v>
+      </c>
+      <c r="EH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ19" t="n">
+        <v>-0.0936555906032636</v>
+      </c>
+      <c r="EK19" t="n">
+        <v>0.01440625611387162</v>
+      </c>
+      <c r="EL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP19" t="n">
+        <v>0.09911425282378976</v>
+      </c>
+      <c r="EQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER19" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES19" t="n">
+        <v>-0.031603826957138</v>
+      </c>
+      <c r="ET19" t="n">
+        <v>0.04917121811385505</v>
+      </c>
+      <c r="EU19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY19" t="n">
+        <v>0.1161634286181202</v>
+      </c>
+      <c r="EZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB19" t="n">
+        <v>-0.02975252028078126</v>
+      </c>
+      <c r="FC19" t="n">
+        <v>-0.08539308654081423</v>
+      </c>
+      <c r="FD19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH19" t="n">
+        <v>0.1194689572166279</v>
+      </c>
+      <c r="FI19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK19" t="n">
+        <v>-0.0003472385826877202</v>
+      </c>
+      <c r="FL19" t="n">
+        <v>-0.150748435708751</v>
+      </c>
+      <c r="FM19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ19" t="n">
+        <v>0.2560767507722128</v>
+      </c>
+      <c r="FR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT19" t="n">
+        <v>-0.008020209947157877</v>
+      </c>
+      <c r="FU19" t="n">
+        <v>-0.106331952621486</v>
+      </c>
+      <c r="FV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ19" t="n">
+        <v>0.07671902844607309</v>
+      </c>
+      <c r="GA19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD19" t="n">
+        <v>-0.008723232390322456</v>
+      </c>
+      <c r="GE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG19" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
